--- a/country_correlation_analysis/country_correlation_Qwen_2_5-3B.xlsx
+++ b/country_correlation_analysis/country_correlation_Qwen_2_5-3B.xlsx
@@ -464,7 +464,7 @@
         <v>0.7685979085120502</v>
       </c>
       <c r="D2" t="n">
-        <v>0.99594980107236</v>
+        <v>0.9959498010723599</v>
       </c>
       <c r="E2" t="n">
         <v>0.636188739367345</v>
@@ -486,7 +486,7 @@
         <v>0.823003914340048</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.004601446850476046</v>
+        <v>-0.004601446850476061</v>
       </c>
     </row>
     <row r="4">
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.99594980107236</v>
+        <v>0.9959498010723599</v>
       </c>
       <c r="C4" t="n">
         <v>0.823003914340048</v>
@@ -518,7 +518,7 @@
         <v>0.636188739367345</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.004601446850476046</v>
+        <v>-0.004601446850476061</v>
       </c>
       <c r="D5" t="n">
         <v>0.5642426780455317</v>

--- a/country_correlation_analysis/country_correlation_Qwen_2_5-3B.xlsx
+++ b/country_correlation_analysis/country_correlation_Qwen_2_5-3B.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,15 +437,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -461,69 +471,143 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7685979085120502</v>
+        <v>0.9894549732780809</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9959498010723599</v>
+        <v>0.9674029540382332</v>
       </c>
       <c r="E2" t="n">
-        <v>0.636188739367345</v>
+        <v>0.9937850439892743</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9937009188595005</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9573945081885665</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7685979085120502</v>
+        <v>0.9894549732780809</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.823003914340048</v>
+        <v>0.993881440599116</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.004601446850476061</v>
+        <v>0.9671824337872582</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9669907843769447</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.90547116449961</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9959498010723599</v>
+        <v>0.9674029540382332</v>
       </c>
       <c r="C4" t="n">
-        <v>0.823003914340048</v>
+        <v>0.993881440599116</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5642426780455317</v>
+        <v>0.9332006584664672</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9329297273238745</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8530542239415013</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.9937850439892743</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9671824337872582</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9332006584664672</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9999997163454472</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9835905825398625</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.9937009188595005</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9669907843769447</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.9329297273238745</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9999997163454472</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9837261919593243</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>0.636188739367345</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.004601446850476061</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.5642426780455317</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="B7" t="n">
+        <v>0.9573945081885665</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.90547116449961</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.8530542239415013</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9835905825398625</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9837261919593243</v>
+      </c>
+      <c r="G7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -538,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,15 +633,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -573,69 +667,143 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4419094591296585</v>
+        <v>0.09253400092269215</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05731654301590607</v>
+        <v>0.1629937996072769</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5610199232543702</v>
+        <v>0.07101324096500204</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.07149274250957982</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1865013775539967</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4419094591296585</v>
+        <v>0.09253400092269215</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3845929161137507</v>
+        <v>0.070459798684586</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9970706176159714</v>
+        <v>0.1635472418876948</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1640267434322711</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.2790353784766888</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05731654301590607</v>
+        <v>0.1629937996072769</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3845929161137507</v>
+        <v>0.070459798684586</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6183364662702778</v>
+        <v>0.2340070405722802</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2344865421168559</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3494951771612738</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.07101324096500204</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.1635472418876948</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2340070405722802</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.000479501544417781</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1154881365889928</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.07149274250957982</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.1640267434322711</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2344865421168559</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.000479501544417781</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.115008635044418</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>0.5610199232543702</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.9970706176159714</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.6183364662702778</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="B7" t="n">
+        <v>0.1865013775539967</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.2790353784766888</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3494951771612738</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.1154881365889928</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.115008635044418</v>
+      </c>
+      <c r="G7" t="n">
         <v>0</v>
       </c>
     </row>
